--- a/data/trans_dic/P8_2_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P8_2_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,41</t>
+          <t>1,42; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,74</t>
+          <t>1,0; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,39</t>
+          <t>0,23; 2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,54</t>
+          <t>1,39; 4,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,62</t>
+          <t>2,07; 5,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,65</t>
+          <t>1,93; 5,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,42</t>
+          <t>0,57; 5,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,81</t>
+          <t>1,69; 3,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,96</t>
+          <t>1,84; 4,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,47</t>
+          <t>1,2; 3,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,83</t>
+          <t>0,73; 3,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,65</t>
+          <t>1,84; 4,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,6</t>
+          <t>2,61; 5,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,37</t>
+          <t>1,5; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,87</t>
+          <t>1,83; 6,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,02</t>
+          <t>3,88; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,39</t>
+          <t>2,84; 6,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,35</t>
+          <t>2,78; 6,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,57</t>
+          <t>0,48; 2,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,52</t>
+          <t>3,21; 5,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,37</t>
+          <t>3,16; 5,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,77</t>
+          <t>2,58; 4,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,62</t>
+          <t>1,36; 3,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,8</t>
+          <t>3,5; 7,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,69</t>
+          <t>4,14; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,27</t>
+          <t>3,89; 7,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,74</t>
+          <t>3,77; 8,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,37</t>
+          <t>5,55; 9,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,34</t>
+          <t>8,59; 13,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,45</t>
+          <t>5,44; 9,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,43</t>
+          <t>4,65; 8,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,72</t>
+          <t>4,96; 7,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,77</t>
+          <t>6,71; 9,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,79</t>
+          <t>5,02; 7,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,57</t>
+          <t>4,8; 7,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,97</t>
+          <t>7,33; 12,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,47</t>
+          <t>8,13; 13,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,81</t>
+          <t>9,62; 15,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 71,3</t>
+          <t>10,43; 72,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,73</t>
+          <t>12,9; 19,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 20,07</t>
+          <t>13,84; 19,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,87</t>
+          <t>12,08; 17,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,1</t>
+          <t>10,11; 15,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,23</t>
+          <t>11,08; 15,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,7</t>
+          <t>11,81; 15,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 15,23</t>
+          <t>11,45; 15,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 55,83</t>
+          <t>11,28; 50,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,6; 29,7</t>
+          <t>20,53; 29,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,87; 24,91</t>
+          <t>16,51; 24,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,4</t>
+          <t>16,6; 24,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,32; 24,96</t>
+          <t>18,2; 24,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,56; 35,48</t>
+          <t>26,77; 36,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,57; 41,45</t>
+          <t>32,11; 41,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,58; 36,55</t>
+          <t>27,84; 36,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,62; 28,22</t>
+          <t>22,68; 28,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,73; 31,28</t>
+          <t>25,03; 31,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,61; 32,21</t>
+          <t>25,42; 32,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,36; 29,5</t>
+          <t>23,09; 29,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,23; 25,73</t>
+          <t>21,32; 25,52</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,66; 40,48</t>
+          <t>29,43; 39,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,4; 48,07</t>
+          <t>35,82; 48,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,46; 39,68</t>
+          <t>29,12; 39,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,21; 29,46</t>
+          <t>22,18; 29,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,06; 66,39</t>
+          <t>56,27; 66,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,34; 64,49</t>
+          <t>53,5; 64,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,42; 53,45</t>
+          <t>42,66; 52,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,37; 41,76</t>
+          <t>11,96; 41,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,93; 52,61</t>
+          <t>45,11; 52,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,97; 54,7</t>
+          <t>46,95; 54,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,76; 45,41</t>
+          <t>37,88; 45,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 34,16</t>
+          <t>13,67; 34,16</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,11; 73,26</t>
+          <t>61,44; 73,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,77; 76,84</t>
+          <t>63,99; 76,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,46; 63,0</t>
+          <t>52,34; 62,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,3; 59,22</t>
+          <t>49,63; 58,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,54; 84,6</t>
+          <t>75,82; 84,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,22; 87,0</t>
+          <t>79,33; 86,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,05; 76,79</t>
+          <t>65,93; 76,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,15; 80,74</t>
+          <t>74,78; 80,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,24; 78,73</t>
+          <t>71,44; 78,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74,91; 81,98</t>
+          <t>75,06; 81,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61,8; 70,05</t>
+          <t>62,53; 70,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,94; 71,02</t>
+          <t>65,93; 71,08</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,84; 15,12</t>
+          <t>12,7; 15,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,38; 16,92</t>
+          <t>14,25; 16,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,3; 15,8</t>
+          <t>13,24; 15,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 38,42</t>
+          <t>14,81; 38,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,77; 24,82</t>
+          <t>21,82; 24,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,1; 27,25</t>
+          <t>24,27; 27,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,43; 24,37</t>
+          <t>21,44; 24,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,73</t>
+          <t>16,86; 22,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,68</t>
+          <t>17,73; 19,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,65</t>
+          <t>19,78; 21,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,71</t>
+          <t>17,73; 19,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,73; 31,44</t>
+          <t>17,66; 29,04</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7308; 21789</t>
+          <t>7030; 20765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3847; 16990</t>
+          <t>4542; 16600</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>969; 10007</t>
+          <t>965; 8971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 24889</t>
+          <t>0; 21349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6898; 21224</t>
+          <t>6477; 20570</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8961; 24183</t>
+          <t>8899; 25024</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8079; 22349</t>
+          <t>7645; 22349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1909; 16964</t>
+          <t>1798; 17474</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16736; 36620</t>
+          <t>16269; 36264</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16112; 35009</t>
+          <t>16258; 36271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10842; 28258</t>
+          <t>9751; 26752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4469; 27343</t>
+          <t>5205; 28405</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13626; 34212</t>
+          <t>13563; 34899</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17704; 38459</t>
+          <t>17930; 38790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9455; 25834</t>
+          <t>8884; 25118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7393; 24851</t>
+          <t>7754; 26177</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24865; 50176</t>
+          <t>24271; 49475</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17532; 38969</t>
+          <t>17310; 39121</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16517; 35774</t>
+          <t>15650; 36441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2444; 13143</t>
+          <t>2444; 13765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44688; 75092</t>
+          <t>43639; 74150</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40503; 69663</t>
+          <t>40957; 70325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29339; 54994</t>
+          <t>29785; 55659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11593; 33904</t>
+          <t>12758; 35211</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22233; 43434</t>
+          <t>22339; 45436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27271; 52283</t>
+          <t>28121; 51754</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26096; 48645</t>
+          <t>26030; 49312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20588; 41506</t>
+          <t>20199; 42893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38225; 64655</t>
+          <t>38269; 65195</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61142; 94799</t>
+          <t>61084; 93518</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35731; 62521</t>
+          <t>35949; 63111</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27984; 49884</t>
+          <t>27494; 50967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66270; 102543</t>
+          <t>65951; 101244</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94948; 135908</t>
+          <t>93331; 136549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66172; 103638</t>
+          <t>66841; 102813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53685; 85329</t>
+          <t>54094; 85832</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38565; 67317</t>
+          <t>38077; 66526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50860; 82767</t>
+          <t>49991; 81788</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60779; 95677</t>
+          <t>62157; 97925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92016; 633027</t>
+          <t>92628; 647332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67309; 101714</t>
+          <t>66503; 99729</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84435; 123641</t>
+          <t>85299; 123119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78189; 116012</t>
+          <t>78378; 114026</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70054; 107641</t>
+          <t>72068; 106979</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>114649; 157623</t>
+          <t>114701; 156373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143224; 193297</t>
+          <t>145346; 193045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>148265; 197302</t>
+          <t>148317; 197788</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>181824; 893693</t>
+          <t>180575; 803883</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>79675; 114836</t>
+          <t>79389; 112195</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72093; 106484</t>
+          <t>70553; 105709</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79878; 116617</t>
+          <t>79331; 118352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102792; 140107</t>
+          <t>102141; 138759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>107306; 143316</t>
+          <t>108131; 145539</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>141358; 185610</t>
+          <t>143776; 185124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>137020; 181600</t>
+          <t>138341; 182030</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123931; 154634</t>
+          <t>124252; 153728</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>195506; 247293</t>
+          <t>197897; 248905</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>224135; 281892</t>
+          <t>222511; 280049</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227685; 287583</t>
+          <t>225080; 286444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>235420; 285399</t>
+          <t>236416; 283086</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86770; 118433</t>
+          <t>86105; 116554</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>112758; 148901</t>
+          <t>110950; 148999</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98477; 132658</t>
+          <t>97345; 131685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81600; 108224</t>
+          <t>81482; 107350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>192242; 227662</t>
+          <t>192957; 227787</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>192345; 228281</t>
+          <t>189393; 227908</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>160230; 201898</t>
+          <t>161164; 200158</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>69195; 254085</t>
+          <t>72750; 252670</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>285530; 334316</t>
+          <t>286660; 334109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>311765; 363121</t>
+          <t>311652; 363178</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>268851; 323360</t>
+          <t>269758; 322956</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123313; 333315</t>
+          <t>133345; 333338</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>128255; 153764</t>
+          <t>128959; 155134</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>161830; 191975</t>
+          <t>159878; 191982</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132249; 161905</t>
+          <t>134522; 160777</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142214; 167450</t>
+          <t>140333; 166694</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>252223; 282475</t>
+          <t>253182; 283128</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>307269; 337481</t>
+          <t>307710; 337289</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>268300; 307304</t>
+          <t>263831; 307350</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>319602; 343365</t>
+          <t>318019; 341804</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>387420; 428128</t>
+          <t>388507; 429028</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>477716; 522814</t>
+          <t>478675; 521541</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>406123; 460371</t>
+          <t>410901; 460071</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>466874; 502856</t>
+          <t>466769; 503268</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>420700; 495339</t>
+          <t>416239; 495773</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>492333; 579094</t>
+          <t>487710; 575578</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>451351; 536199</t>
+          <t>449509; 537346</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>512669; 1328973</t>
+          <t>512202; 1322235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>735747; 838704</t>
+          <t>737279; 836512</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>857459; 969377</t>
+          <t>863317; 968987</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>759547; 863753</t>
+          <t>760064; 861693</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>627069; 843638</t>
+          <t>625698; 843437</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1178324; 1310043</t>
+          <t>1180066; 1302736</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1378450; 1511431</t>
+          <t>1380738; 1515148</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1227561; 1367649</t>
+          <t>1230276; 1365649</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1271347; 2254535</t>
+          <t>1265988; 2082517</t>
         </is>
       </c>
     </row>
